--- a/docs/sap490/generated/Test_Report_IDTS_SAP01_vi_v0.3.xlsx
+++ b/docs/sap490/generated/Test_Report_IDTS_SAP01_vi_v0.3.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Cover!$A$1:$F$17</definedName>
-    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Feature 1'!$A$1:$O$23</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'Feature 1'!$A$1:$O$32</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">'Feature 1'!$1:$10</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'Feature 2'!$A$1:$O$26</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">'Feature 2'!$1:$10</definedName>
@@ -167,7 +167,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="305">
   <si>
     <t xml:space="preserve">TÀI LIỆU BÁO CÁO KIỂM THỬ</t>
   </si>
@@ -343,11 +343,8 @@
     <t xml:space="preserve">FT-DUP-001 — Hỗ trợ kiểm tra trùng trước khi tạo</t>
   </si>
   <si>
-    <t xml:space="preserve">Feature 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">SRS-FR-BUG-003
-FUNCTIONAL_UI_API / NOT_RUN</t>
+FUNCTIONAL_UI_API / PASSED</t>
   </si>
   <si>
     <t xml:space="preserve">Tester đã đăng nhập; có ít nhất một bug tương tự và một bug không liên quan.</t>
@@ -357,7 +354,7 @@
   </si>
   <si>
     <t xml:space="preserve">SRS-FR-CLASS-001, SRS-FR-CLASS-004, SRS-FR-ASSIGN-001
-FUNCTIONAL_UI_API / NOT_RUN</t>
+FUNCTIONAL_UI_API / PASSED</t>
   </si>
   <si>
     <t xml:space="preserve">Có classification pair và Developer Responsibility active.</t>
@@ -367,7 +364,7 @@
   </si>
   <si>
     <t xml:space="preserve">SRS-FR-ASSIGN-003, SRS-FR-STATUS-009
-FUNCTIONAL_UI_API / NOT_RUN</t>
+FUNCTIONAL_UI_API / PASSED</t>
   </si>
   <si>
     <t xml:space="preserve">Tester đã đăng nhập và mọi field bắt buộc hợp lệ.</t>
@@ -377,7 +374,7 @@
   </si>
   <si>
     <t xml:space="preserve">SRS-FR-ASSIGN-004, SRS-FR-AUDIT-001
-FUNCTIONAL_UI_API / NOT_RUN</t>
+FUNCTIONAL_UI_API / PASSED</t>
   </si>
   <si>
     <t xml:space="preserve">Có bug đã assign và Developer phù hợp thứ hai.</t>
@@ -387,7 +384,7 @@
   </si>
   <si>
     <t xml:space="preserve">SRS-FR-STATUS-001, SRS-FR-STATUS-002, SRS-FR-STATUS-009
-FUNCTIONAL_UI_API / NOT_RUN</t>
+FUNCTIONAL_UI_API / PASSED</t>
   </si>
   <si>
     <t xml:space="preserve">Bug đã assign; có account Developer được assign và không được assign.</t>
@@ -397,7 +394,7 @@
   </si>
   <si>
     <t xml:space="preserve">SRS-FR-STATUS-003, SRS-FR-STATUS-004, SRS-FR-STATUS-009
-FUNCTIONAL_UI_API / NOT_RUN</t>
+FUNCTIONAL_UI_API / PASSED</t>
   </si>
   <si>
     <t xml:space="preserve">Bug đã assign nhưng classification hoặc owner không phù hợp.</t>
@@ -407,7 +404,7 @@
   </si>
   <si>
     <t xml:space="preserve">SRS-FR-STATUS-005, SRS-FR-STATUS-006, SRS-FR-STATUS-007, SRS-FR-STATUS-008
-FUNCTIONAL_UI_API / NOT_RUN</t>
+FUNCTIONAL_UI_API / PASSED</t>
   </si>
   <si>
     <t xml:space="preserve">Bug đang In Progress và tái hiện được.</t>
@@ -427,7 +424,7 @@
   </si>
   <si>
     <t xml:space="preserve">SRS-DATA-007, SRS-FR-AUDIT-001
-FUNCTIONAL_HTTP_UI / NOT_RUN</t>
+FUNCTIONAL_HTTP_UI / PASSED</t>
   </si>
   <si>
     <t xml:space="preserve">Tester đã đăng nhập, có bug và file evidence nhỏ được phép.</t>
@@ -457,13 +454,16 @@
   </si>
   <si>
     <t xml:space="preserve">SRS-FR-AI-002, SRS-FR-AI-003
-FUNCTIONAL_UI_API / NOT_RUN</t>
+FUNCTIONAL_UI_API / PASSED</t>
   </si>
   <si>
     <t xml:space="preserve">User đã đăng nhập; có mode AI disabled và suggestion có kiểm soát.</t>
   </si>
   <si>
     <t xml:space="preserve">UAT-001 — Tạo và phân loại bug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feature 2</t>
   </si>
   <si>
     <t xml:space="preserve">SRS-FR-BUG-001, SRS-FR-BUG-002, SRS-FR-CLASS-003, SRS-FR-ASSIGN-003
@@ -532,7 +532,7 @@
     <t xml:space="preserve">Ghi chú</t>
   </si>
   <si>
-    <t xml:space="preserve">27 kế hoạch; 12 đã chạy; 12 đạt; 0 không đạt; 0 bị chặn; 15 Chưa chạy/Prepared. Pending không phải Passed.</t>
+    <t xml:space="preserve">27 kế hoạch; 21 đã chạy; 21 đạt; 0 không đạt; 0 bị chặn; 6 Chưa chạy/Prepared. Pending không phải Passed.</t>
   </si>
   <si>
     <t xml:space="preserve">Mã phân hệ</t>
@@ -586,7 +586,7 @@
     <t xml:space="preserve">Case đã thực thi</t>
   </si>
   <si>
-    <t xml:space="preserve">12 Passed + 0 Failed</t>
+    <t xml:space="preserve">21 Passed + 0 Failed</t>
   </si>
   <si>
     <t xml:space="preserve">Đạt</t>
@@ -607,7 +607,7 @@
     <t xml:space="preserve">Chưa chạy / Đang chờ</t>
   </si>
   <si>
-    <t xml:space="preserve">9 NOT_RUN + 6 PREPARED</t>
+    <t xml:space="preserve">0 NOT_RUN + 6 PREPARED</t>
   </si>
   <si>
     <t xml:space="preserve">Truy vết requirement theo kế hoạch</t>
@@ -619,9 +619,6 @@
     <t xml:space="preserve">Coverage requirement đã thực thi</t>
   </si>
   <si>
-    <t xml:space="preserve">17 / 32</t>
-  </si>
-  <si>
     <t xml:space="preserve">Số assertion/check tự động</t>
   </si>
   <si>
@@ -826,6 +823,117 @@
     <t xml:space="preserve">Thực tế: 28 đạt, 0 lỗi, 0 bỏ qua; exit code 0. | Bằng chứng: scripts/qa/test-auth-foundation-programmatic.js | Defect: IDTS-35, IDTS-52, IDTS-53 | Giới hạn: Chưa có UAT browser login/profile hiện tại và không claim identity provider production. | Điều kiện sau: Session test được revoke hoặc chỉ còn trong database in-memory.</t>
   </si>
   <si>
+    <t xml:space="preserve">FT-DUP-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hỗ trợ kiểm tra trùng trước khi tạo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Req: SRS-FR-BUG-003 | Vai trò: Tester | Dữ liệu: Mô tả lỗi login mới và classification context. | 1) Mở Create Bug. | 2) Chạy kiểm tra bug tương tự. | 3) Review candidate và bỏ qua suggestion. | 4) Xác nhận không có DuplicateLinks mới và tiếp tục create.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candidate liên quan hiển thị dạng gợi ý; bỏ qua không đổi dữ liệu hoặc chặn create.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-24T20:42:48+07:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDTS-100 automated acceptance under DonHV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thực tế: ??t tr?n Render Shared QA. API v? h?p tho?i Fiori tr? g?i ? tr?ng l?p ch? ?? review, bao ph? tr?ng th?i kh?ng c? k?t qu? v? kh?ng thay ??i d? li?u workflow c?a Bug. | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-ai/render-ai-smoke.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/all-review-actions/shared-qa-ai-browser.json | Defect: None | Giới hạn: Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng. | Điều kiện sau: Không có quan hệ duplicate tự động.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT-CLASS-ASSIGN-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phân loại và assign theo responsibility active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Req: SRS-FR-CLASS-001, SRS-FR-CLASS-004, SRS-FR-ASSIGN-001 | Vai trò: Tester | Dữ liệu: Application Component=Bug Management; Defect Category=Fiori/UI5; một Developer phù hợp và một không phù hợp. | 1) Mở Create Bug. | 2) Chọn Application Component và Defect Category. | 3) Mở candidate Smart Assign/Assignee. | 4) Chọn Developer phù hợp và lưu. | 5) Reload bug.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chỉ candidate active có responsibility được chọn; bug lưu ở Assigned và ownership còn sau reload.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thực tế: ??t tr?n Render Shared QA. Mapping ph?n lo?i active ???c ch?p nh?n, Developer ph? h?p ???c assign, Developer t? assign qua API b? ch?n, v? Smart Assign v?n gi? quy?t ??nh th? c?ng. | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/assignment/idts72-ai-browser-smoke.json | Defect: IDTS-56 | Giới hạn: Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng. | Điều kiện sau: Developer được assign là technical owner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT-PENDING-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tạo bug không có assignee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Req: SRS-FR-ASSIGN-003, SRS-FR-STATUS-009 | Vai trò: Tester | Dữ liệu: Bug hợp lệ nhưng không chọn assignee. | 1) Tạo bug hợp lệ. | 2) Không chọn assignee. | 3) Submit và reload. | 4) Kiểm tra status và Current Action Owner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bug ở Pending Assignment; không Developer nào được tự chọn; PM/Tester queue nhận action tiếp theo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thực tế: ??t tr?n Render Shared QA. Activate draft h?p l? kh?ng c? assignee t?o tr?ng th?i PENDING_ASSIGNMENT, kh?ng c? assignee v? PM l? vai tr? x? l? ti?p theo. | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json | Defect: None | Giới hạn: Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng. | Điều kiện sau: Bug chờ assignment rõ ràng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT-REASSIGN-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reassign có history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Req: SRS-FR-ASSIGN-004, SRS-FR-AUDIT-001 | Vai trò: Tester / PM | Dữ liệu: Lý do: cân bằng workload. | 1) Mở bug đã assign. | 2) Chọn Developer phù hợp khác. | 3) Lưu kèm lý do reassign. | 4) Reload ownership và History.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chỉ còn một assignee; history có actor, owner cũ/mới, lý do và timestamp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thực tế: ??t tr?n Render Shared QA. Bug ?i t? Rejected v? Pending Assignment, x?a assignee, ???c assign l?i v? gi? ??ng action type trong history. | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json | Defect: None | Giới hạn: Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng. | Điều kiện sau: Developer mới là technical owner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT-DEV-INFO-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer review và Request More Information</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Req: SRS-FR-STATUS-001, SRS-FR-STATUS-002, SRS-FR-STATUS-009 | Vai trò: Developer | Dữ liệu: Lý do: thiếu phiên bản browser và bước tái hiện chính xác. | 1) Mở bằng Developer không được assign và thử action. | 2) Mở bằng Developer được assign và gửi reason rỗng. | 3) Gửi reason hợp lệ. | 4) Reload status, owner, notification và history.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sai role/owner và reason rỗng bị chặn; action hợp lệ set Need More Information và Tester action owner cùng audit/notification.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thực tế: ??t tr?n Render Shared QA. Developer ???c assign y?u c?u th?m th?ng tin, reason r?ng tr? 400 v? Tester resubmit Bug v? ??ng Developer. | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json, docs/pm/evidence/idts-100/shared-qa-email-brevo-20260724.md | Defect: None | Giới hạn: Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng. | Điều kiện sau: Tester phải bổ sung thông tin và resubmit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT-REJECT-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reject, sửa và reassign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Req: SRS-FR-STATUS-003, SRS-FR-STATUS-004, SRS-FR-STATUS-009 | Vai trò: Developer / Tester | Dữ liệu: Lý do: component là Notification, không phải Dashboard. | 1) Reject không reason và xác nhận validation. | 2) Reject với reason cụ thể. | 3) Reload status/history/current owner. | 4) Bằng Tester, sửa classification và reassign hoặc chọn Pending Assignment. | 5) Reload lại.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason rỗng bị chặn; rejection hợp lệ ghi follow-up; sau sửa rời Rejected qua Assigned hoặc Pending Assignment, không đi thẳng Need More Information.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thực tế: ??t tr?n Render Shared QA. Developer ???c assign reject k?m l? do; PM ??a Bug v? h?ng ??i assignment v? ho?n t?t correction follow-up b?ng reassign. | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json, docs/pm/evidence/idts-100/shared-qa-email-brevo-20260724.md | Defect: None | Giới hạn: Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng. | Điều kiện sau: Bug có technical/queue owner tiếp theo rõ ràng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT-LIFECYCLE-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolve, retest, close và reopen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Req: SRS-FR-STATUS-005, SRS-FR-STATUS-006, SRS-FR-STATUS-007, SRS-FR-STATUS-008 | Vai trò: Developer / Tester / PM | Dữ liệu: Resolution note cùng một observation retest pass và một fail. | 1) Developer resolve kèm note. | 2) Tester/PM chuyển Retest Required. | 3) Ghi retest pass và close; reload. | 4) Trên bug thứ hai, ghi retest fail và reopen; reload.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass đến Closed; fail đến Reopened; note bắt buộc, owner và audit nhất quán sau reload.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thực tế: ??t tr?n Render Shared QA v?i session PM, Tester v? Developer: assign, review, progress, y?u c?u th?ng tin, resubmit, resolve, retest, close, reopen, reject v? reassign ??u persist c?ng history ch?nh x?c v? notification side effect. | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json, docs/pm/evidence/idts-100/shared-qa-email-brevo-20260724.md | Defect: None | Giới hạn: Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng. | Điều kiện sau: Closed không có next processor; Reopened quay lại xử lý active.</t>
+  </si>
+  <si>
     <t xml:space="preserve">FT-COMMENT-001</t>
   </si>
   <si>
@@ -844,6 +952,21 @@
     <t xml:space="preserve">Thực tế: Đạt: row được tạo và còn sau reconnect. | Bằng chứng: scripts/qa/test-comments-attachments-programmatic.js | Defect: IDTS-55 | Giới hạn: Chưa có evidence visual comment Fiori mới. | Điều kiện sau: Test database nằm trong .tmp bị ignore.</t>
   </si>
   <si>
+    <t xml:space="preserve">FT-ATTACH-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upload, download, reload và xóa attachment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Req: SRS-DATA-007, SRS-FR-AUDIT-001 | Vai trò: Tester | Dữ liệu: File text/image nhỏ, biến thể MIME không cho phép và file vượt giới hạn. | 1) Edit root draft và upload evidence hợp lệ. | 2) Activate và reload. | 3) Download và so sánh nội dung. | 4) Thử biến thể MIME/size sai. | 5) Xóa và kiểm tra cleanup metadata/object/history.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence hợp lệ persist và download được; biến thể sai bị chặn; delete dọn storage và ghi history.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thực tế: ??t tr?n Render Shared QA. Hai file ch?n tr??c khi save ???c upload sau activation, download c? SHA-256 kh?p, c?n sau redeploy; m?t attachment ???c x?a v? l?n download sau tr? 404. | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-attachments/idts73-create-attachments-browser.json, docs/pm/evidence/idts-100/shared-qa-attachments/delete-verification-20260724.md | Defect: IDTS-55 | Giới hạn: Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng. | Điều kiện sau: Không còn attachment mồ côi.</t>
+  </si>
+  <si>
     <t xml:space="preserve">FT-NOTIF-001</t>
   </si>
   <si>
@@ -880,144 +1003,24 @@
     <t xml:space="preserve">Thực tế: Đạt 20/20. | Bằng chứng: scripts/qa/test-pm-monitoring-programmatic.js | Defect: None | Giới hạn: Chưa check visual/UX dashboard mới. | Điều kiện sau: Monitoring read-only không đổi business data.</t>
   </si>
   <si>
+    <t xml:space="preserve">FT-AI-REVIEW-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con người review AI suggestion mà không tự động mutation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Req: SRS-FR-AI-002, SRS-FR-AI-003 | Vai trò: Tester / PM | Dữ liệu: Suggestion similar/classification/handoff với biến thể safe và malformed. | 1) Ghi giá trị bug trước suggestion. | 2) Mở review suggestion. | 3) Bỏ qua và reload. | 4) Lặp lại mode failure/malformed. | 5) Xác nhận giá trị bug không đổi và audit/feedback an toàn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggestion không tự đổi assignment, classification hoặc lifecycle; workflow bình thường vẫn dùng được.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thực tế: ??t acceptance khi provider b? t?t tr?n Render Shared QA. Similar Bugs, Classification, Handoff Summary v? Smart Assignment ??u ch? ?? review, an to?n, hi?n th? tr?n browser v? kh?ng thay ??i workflow. OpenAI live v?n NOT ACCEPTED theo quy?t ??nh. | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-ai/render-ai-smoke.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/all-review-actions/shared-qa-ai-browser.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/assignment/idts72-ai-browser-smoke.json | Defect: IDTS-78 | Giới hạn: Evidence acceptance do agent th?c thi; x?c nh?n UAT ch?nh th?c c?a con ng??i ???c theo d?i ri?ng. | Điều kiện sau: Bug không đổi trừ khi user có quyền thực hiện action bình thường riêng.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Flow UI manual vẫn NOT_RUN và UAT vẫn PREPARED; không claim sign-off.</t>
   </si>
   <si>
-    <t xml:space="preserve">FT-DUP-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hỗ trợ kiểm tra trùng trước khi tạo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Req: SRS-FR-BUG-003 | Vai trò: Tester | Dữ liệu: Mô tả lỗi login mới và classification context. | 1) Mở Create Bug. | 2) Chạy kiểm tra bug tương tự. | 3) Review candidate và bỏ qua suggestion. | 4) Xác nhận không có DuplicateLinks mới và tiếp tục create.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Candidate liên quan hiển thị dạng gợi ý; bỏ qua không đổi dữ liệu hoặc chặn create.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: N/A | Defect: None | Giới hạn: Chưa chạy mới duplicate review UI/API trong remediation này. | Điều kiện sau: Không có quan hệ duplicate tự động.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT-CLASS-ASSIGN-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phân loại và assign theo responsibility active</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Req: SRS-FR-CLASS-001, SRS-FR-CLASS-004, SRS-FR-ASSIGN-001 | Vai trò: Tester | Dữ liệu: Application Component=Bug Management; Defect Category=Fiori/UI5; một Developer phù hợp và một không phù hợp. | 1) Mở Create Bug. | 2) Chọn Application Component và Defect Category. | 3) Mở candidate Smart Assign/Assignee. | 4) Chọn Developer phù hợp và lưu. | 5) Reload bug.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chỉ candidate active có responsibility được chọn; bug lưu ở Assigned và ownership còn sau reload.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: N/A | Defect: IDTS-56 | Giới hạn: Cần evidence browser và persistence mới. | Điều kiện sau: Developer được assign là technical owner.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT-PENDING-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tạo bug không có assignee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Req: SRS-FR-ASSIGN-003, SRS-FR-STATUS-009 | Vai trò: Tester | Dữ liệu: Bug hợp lệ nhưng không chọn assignee. | 1) Tạo bug hợp lệ. | 2) Không chọn assignee. | 3) Submit và reload. | 4) Kiểm tra status và Current Action Owner.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bug ở Pending Assignment; không Developer nào được tự chọn; PM/Tester queue nhận action tiếp theo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: N/A | Defect: None | Giới hạn: Cần evidence create/reload mới. | Điều kiện sau: Bug chờ assignment rõ ràng.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT-REASSIGN-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reassign có history</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Req: SRS-FR-ASSIGN-004, SRS-FR-AUDIT-001 | Vai trò: Tester / PM | Dữ liệu: Lý do: cân bằng workload. | 1) Mở bug đã assign. | 2) Chọn Developer phù hợp khác. | 3) Lưu kèm lý do reassign. | 4) Reload ownership và History.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chỉ còn một assignee; history có actor, owner cũ/mới, lý do và timestamp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: N/A | Defect: None | Giới hạn: Quyền PM reassign trực tiếp vẫn phụ thuộc decision đã ghi; chạy bằng role runtime hiện cho phép. | Điều kiện sau: Developer mới là technical owner.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT-DEV-INFO-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer review và Request More Information</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Req: SRS-FR-STATUS-001, SRS-FR-STATUS-002, SRS-FR-STATUS-009 | Vai trò: Developer | Dữ liệu: Lý do: thiếu phiên bản browser và bước tái hiện chính xác. | 1) Mở bằng Developer không được assign và thử action. | 2) Mở bằng Developer được assign và gửi reason rỗng. | 3) Gửi reason hợp lệ. | 4) Reload status, owner, notification và history.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sai role/owner và reason rỗng bị chặn; action hợp lệ set Need More Information và Tester action owner cùng audit/notification.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: N/A | Defect: None | Giới hạn: Cần evidence role matrix và reload mới. | Điều kiện sau: Tester phải bổ sung thông tin và resubmit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT-REJECT-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reject, sửa và reassign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Req: SRS-FR-STATUS-003, SRS-FR-STATUS-004, SRS-FR-STATUS-009 | Vai trò: Developer / Tester | Dữ liệu: Lý do: component là Notification, không phải Dashboard. | 1) Reject không reason và xác nhận validation. | 2) Reject với reason cụ thể. | 3) Reload status/history/current owner. | 4) Bằng Tester, sửa classification và reassign hoặc chọn Pending Assignment. | 5) Reload lại.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reason rỗng bị chặn; rejection hợp lệ ghi follow-up; sau sửa rời Rejected qua Assigned hoặc Pending Assignment, không đi thẳng Need More Information.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: N/A | Defect: None | Giới hạn: Cần evidence lifecycle UI/API đầy đủ. | Điều kiện sau: Bug có technical/queue owner tiếp theo rõ ràng.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT-LIFECYCLE-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resolve, retest, close và reopen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Req: SRS-FR-STATUS-005, SRS-FR-STATUS-006, SRS-FR-STATUS-007, SRS-FR-STATUS-008 | Vai trò: Developer / Tester / PM | Dữ liệu: Resolution note cùng một observation retest pass và một fail. | 1) Developer resolve kèm note. | 2) Tester/PM chuyển Retest Required. | 3) Ghi retest pass và close; reload. | 4) Trên bug thứ hai, ghi retest fail và reopen; reload.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pass đến Closed; fail đến Reopened; note bắt buộc, owner và audit nhất quán sau reload.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: N/A | Defect: None | Giới hạn: Chưa chạy mới full lifecycle trong remediation này. | Điều kiện sau: Closed không có next processor; Reopened quay lại xử lý active.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT-ATTACH-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upload, download, reload và xóa attachment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Req: SRS-DATA-007, SRS-FR-AUDIT-001 | Vai trò: Tester | Dữ liệu: File text/image nhỏ, biến thể MIME không cho phép và file vượt giới hạn. | 1) Edit root draft và upload evidence hợp lệ. | 2) Activate và reload. | 3) Download và so sánh nội dung. | 4) Thử biến thể MIME/size sai. | 5) Xóa và kiểm tra cleanup metadata/object/history.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evidence hợp lệ persist và download được; biến thể sai bị chặn; delete dọn storage và ghi history.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: scripts/qa/test-comments-attachments.ps1 | Defect: IDTS-55 | Giới hạn: Command HTTP bắt buộc chưa chạy trong remediation; suite comments programmatic chỉ in note attachment. | Điều kiện sau: Không còn attachment mồ côi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT-AI-REVIEW-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Con người review AI suggestion mà không tự động mutation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Req: SRS-FR-AI-002, SRS-FR-AI-003 | Vai trò: Tester / PM | Dữ liệu: Suggestion similar/classification/handoff với biến thể safe và malformed. | 1) Ghi giá trị bug trước suggestion. | 2) Mở review suggestion. | 3) Bỏ qua và reload. | 4) Lặp lại mode failure/malformed. | 5) Xác nhận giá trị bug không đổi và audit/feedback an toàn.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suggestion không tự đổi assignment, classification hoặc lifecycle; workflow bình thường vẫn dùng được.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: N/A | Defect: IDTS-78 | Giới hạn: REG-AI-20260723 chỉ chứng minh provider safety, không phải full business flow human-review này. | Điều kiện sau: Bug không đổi trừ khi user có quyền thực hiện action bình thường riêng.</t>
-  </si>
-  <si>
     <t xml:space="preserve">UAT-001</t>
   </si>
   <si>
@@ -1030,7 +1033,7 @@
     <t xml:space="preserve">Assigned/Pending Assignment khớp lựa chọn; không tự chọn Developer; dữ liệu persist.</t>
   </si>
   <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: N/A | Defect: None | Giới hạn: Actual result, decision, tester/date và sign-off cố ý để trống tới khi UAT. | Điều kiện sau: Bug UAT được đánh dấu để cleanup.</t>
+    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json, docs/pm/evidence/idts-100/shared-qa-attachments/idts73-create-attachments-browser.json | Defect: None | Giới hạn: PREPARED ? v?n c?n ng??i th?t th?c thi, ??a ra quy?t ??nh, ng?y v? ch? k?. | Điều kiện sau: Bug UAT được đánh dấu để cleanup.</t>
   </si>
   <si>
     <t xml:space="preserve">UAT-002</t>
@@ -1045,7 +1048,7 @@
     <t xml:space="preserve">Reason bắt buộc, transition hợp lệ, notification, history và Current Action Owner đúng.</t>
   </si>
   <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: N/A | Defect: None | Giới hạn: Không claim execution/sign-off. | Điều kiện sau: Cả hai bug có next owner rõ ràng.</t>
+    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json, docs/pm/evidence/idts-100/shared-qa-email-brevo-20260724.md | Defect: None | Giới hạn: PREPARED ? v?n c?n ng??i th?t th?c thi, ??a ra quy?t ??nh, ng?y v? ch? k?. | Điều kiện sau: Cả hai bug có next owner rõ ràng.</t>
   </si>
   <si>
     <t xml:space="preserve">UAT-003</t>
@@ -1057,7 +1060,7 @@
     <t xml:space="preserve">Pass đóng; fail mở lại; không xuất hiện nhánh request information không được hỗ trợ sau retest.</t>
   </si>
   <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: N/A | Defect: None | Giới hạn: Không claim execution/sign-off. | Điều kiện sau: Một bug UAT Closed và một Reopened.</t>
+    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json, docs/pm/evidence/idts-100/shared-qa-email-brevo-20260724.md | Defect: None | Giới hạn: PREPARED ? v?n c?n ng??i th?t th?c thi, ??a ra quy?t ??nh, ng?y v? ch? k?. | Điều kiện sau: Một bug UAT Closed và một Reopened.</t>
   </si>
   <si>
     <t xml:space="preserve">UAT-004</t>
@@ -1072,7 +1075,7 @@
     <t xml:space="preserve">Comment và evidence persist; download được; cleanup và history đúng.</t>
   </si>
   <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: N/A | Defect: None | Giới hạn: Không claim execution/sign-off. | Điều kiện sau: Attachment được cleanup theo kế hoạch UAT.</t>
+    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-attachments/idts73-create-attachments-browser.json, docs/pm/evidence/idts-100/shared-qa-attachments/delete-verification-20260724.md | Defect: None | Giới hạn: PREPARED ? v?n c?n ng??i th?t th?c thi, ??a ra quy?t ??nh, ng?y v? ch? k?. | Điều kiện sau: Attachment được cleanup theo kế hoạch UAT.</t>
   </si>
   <si>
     <t xml:space="preserve">UAT-005</t>
@@ -1087,7 +1090,7 @@
     <t xml:space="preserve">Count, filter và wording owner dễ hiểu và nhất quán sau reload.</t>
   </si>
   <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: N/A | Defect: None | Giới hạn: Không claim execution/sign-off. | Điều kiện sau: Monitoring vẫn read-only.</t>
+    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-lifecycle/shared-qa-lifecycle.json, docs/pm/evidence/idts-100/local-fast/ | Defect: None | Giới hạn: PREPARED ? v?n c?n ng??i th?t th?c thi, ??a ra quy?t ??nh, ng?y v? ch? k?. | Điều kiện sau: Monitoring vẫn read-only.</t>
   </si>
   <si>
     <t xml:space="preserve">UAT-006</t>
@@ -1102,7 +1105,7 @@
     <t xml:space="preserve">Không mutation tự động; hiển thị message an toàn; action bình thường vẫn dùng được.</t>
   </si>
   <si>
-    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: N/A | Defect: None | Giới hạn: Không claim execution/sign-off và không yêu cầu provider live. | Điều kiện sau: Bug test vẫn do con người kiểm soát.</t>
+    <t xml:space="preserve">Thực tế: Chưa chạy | Bằng chứng: docs/pm/evidence/idts-100/shared-qa-ai/render-ai-smoke.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/all-review-actions/shared-qa-ai-browser.json, docs/pm/evidence/idts-100/shared-qa-ai-browser/assignment/idts72-ai-browser-smoke.json | Defect: None | Giới hạn: PREPARED ? v?n c?n ng??i th?t th?c thi, ??a ra quy?t ??nh, ng?y v? ch? k?. | Điều kiện sau: Bug test vẫn do con người kiểm soát.</t>
   </si>
 </sst>
 </file>
@@ -1681,212 +1684,212 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="149">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="3" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="3" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="2" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="3" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="3" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="4" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="4" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="6" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="6" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="8" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="8" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="8" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="8" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="23" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="7" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="7" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="8" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="8" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="9" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="9" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="10" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="10" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="11" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="11" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="11" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="11" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="12" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="12" xfId="23" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="169" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1894,392 +1897,388 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="2" borderId="8" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="2" borderId="8" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="8" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="8" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="21" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="3" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="3" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="5" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="5" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="23" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="23" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="24" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="24" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="2" borderId="25" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="25" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="25" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="25" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="3" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="3" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="26" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="26" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="26" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="26" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="2" borderId="27" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="27" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="28" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="28" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="29" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="29" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="3" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="3" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="7" borderId="30" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="7" borderId="30" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="30" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="30" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="31" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="31" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="32" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="32" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="0" xfId="22" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="3" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="30" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="30" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="1" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="33" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="33" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="33" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="33" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2370,9 +2369,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>199800</xdr:colOff>
+      <xdr:colOff>199440</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>786960</xdr:rowOff>
+      <xdr:rowOff>786600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2386,7 +2385,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="114480" y="250920"/>
-          <a:ext cx="2133360" cy="698040"/>
+          <a:ext cx="2133360" cy="697680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2585,448 +2584,448 @@
   <dimension ref="A2:F17"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="256" min="7" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="257" min="257" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="257" min="257" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="258" min="258" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="259" min="259" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="260" min="260" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="261" min="261" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="262" min="262" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="512" min="263" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="513" min="513" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="513" min="513" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="514" min="514" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="515" min="515" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="516" min="516" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="517" min="517" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="518" min="518" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="768" min="519" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="769" min="769" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="769" min="769" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="770" min="770" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="771" min="771" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="772" min="772" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="773" min="773" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="774" min="774" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="775" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1025" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="1025" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1026" min="1026" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1027" min="1027" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1028" min="1028" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1029" min="1029" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1030" min="1030" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1280" min="1031" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1281" min="1281" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1281" min="1281" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1282" min="1282" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1283" min="1283" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1284" min="1284" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1285" min="1285" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1286" min="1286" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1536" min="1287" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1537" min="1537" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1537" min="1537" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1538" min="1538" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1539" min="1539" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1540" min="1540" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1541" min="1541" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1542" min="1542" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1792" min="1543" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1793" min="1793" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1793" min="1793" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1794" min="1794" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1795" min="1795" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1796" min="1796" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1797" min="1797" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1798" min="1798" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2048" min="1799" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2049" min="2049" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2049" min="2049" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2050" min="2050" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2051" min="2051" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2052" min="2052" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2053" min="2053" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2054" min="2054" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2304" min="2055" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2305" min="2305" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2305" min="2305" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2306" min="2306" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2307" min="2307" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2308" min="2308" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2309" min="2309" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2310" min="2310" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2560" min="2311" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2561" min="2561" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2561" min="2561" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2562" min="2562" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2563" min="2563" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2564" min="2564" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2565" min="2565" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2566" min="2566" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2816" min="2567" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2817" min="2817" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2817" min="2817" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2818" min="2818" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2819" min="2819" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2820" min="2820" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2821" min="2821" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2822" min="2822" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3072" min="2823" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3073" min="3073" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3073" min="3073" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3074" min="3074" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3075" min="3075" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3076" min="3076" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3077" min="3077" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3078" min="3078" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3328" min="3079" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3329" min="3329" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3329" min="3329" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3330" min="3330" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3331" min="3331" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3332" min="3332" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3333" min="3333" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3334" min="3334" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3584" min="3335" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3585" min="3585" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3585" min="3585" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3586" min="3586" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3587" min="3587" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3588" min="3588" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3589" min="3589" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3590" min="3590" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3840" min="3591" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3841" min="3841" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3841" min="3841" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3842" min="3842" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3843" min="3843" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3844" min="3844" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3845" min="3845" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3846" min="3846" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4096" min="3847" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4097" min="4097" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4097" min="4097" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4098" min="4098" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4099" min="4099" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4100" min="4100" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4101" min="4101" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4102" min="4102" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4352" min="4103" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4353" min="4353" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4353" min="4353" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4354" min="4354" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4355" min="4355" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4356" min="4356" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4357" min="4357" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4358" min="4358" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4608" min="4359" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4609" min="4609" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4609" min="4609" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4610" min="4610" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4611" min="4611" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4612" min="4612" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4613" min="4613" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4614" min="4614" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="4864" min="4615" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4865" min="4865" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4865" min="4865" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4866" min="4866" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4867" min="4867" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4868" min="4868" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4869" min="4869" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4870" min="4870" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5120" min="4871" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5121" min="5121" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5121" min="5121" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5122" min="5122" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5123" min="5123" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5124" min="5124" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5125" min="5125" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5126" min="5126" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5376" min="5127" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5377" min="5377" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5377" min="5377" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5378" min="5378" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5379" min="5379" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5380" min="5380" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5381" min="5381" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5382" min="5382" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5632" min="5383" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5633" min="5633" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5633" min="5633" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5634" min="5634" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5635" min="5635" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5636" min="5636" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5637" min="5637" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5638" min="5638" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5888" min="5639" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5889" min="5889" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5889" min="5889" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5890" min="5890" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5891" min="5891" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5892" min="5892" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5893" min="5893" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5894" min="5894" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6144" min="5895" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6145" min="6145" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6145" min="6145" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6146" min="6146" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6147" min="6147" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6148" min="6148" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6149" min="6149" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6150" min="6150" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6400" min="6151" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6401" min="6401" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6401" min="6401" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6402" min="6402" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6403" min="6403" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6404" min="6404" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6405" min="6405" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6406" min="6406" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6656" min="6407" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6657" min="6657" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6657" min="6657" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6658" min="6658" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6659" min="6659" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6660" min="6660" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6661" min="6661" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6662" min="6662" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6912" min="6663" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6913" min="6913" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6913" min="6913" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6914" min="6914" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6915" min="6915" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6916" min="6916" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6917" min="6917" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6918" min="6918" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7168" min="6919" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7169" min="7169" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7169" min="7169" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7170" min="7170" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7171" min="7171" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7172" min="7172" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7173" min="7173" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7174" min="7174" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7424" min="7175" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7425" min="7425" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7425" min="7425" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7426" min="7426" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7427" min="7427" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7428" min="7428" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7429" min="7429" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7430" min="7430" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7680" min="7431" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7681" min="7681" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7681" min="7681" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7682" min="7682" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7683" min="7683" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7684" min="7684" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7685" min="7685" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7686" min="7686" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="7936" min="7687" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7937" min="7937" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7937" min="7937" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7938" min="7938" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7939" min="7939" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7940" min="7940" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7941" min="7941" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7942" min="7942" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8192" min="7943" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8193" min="8193" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8193" min="8193" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8194" min="8194" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8195" min="8195" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8196" min="8196" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8197" min="8197" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8198" min="8198" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8448" min="8199" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8449" min="8449" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8449" min="8449" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8450" min="8450" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8451" min="8451" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8452" min="8452" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8453" min="8453" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8454" min="8454" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8704" min="8455" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8705" min="8705" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8705" min="8705" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8706" min="8706" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8707" min="8707" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8708" min="8708" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8709" min="8709" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8710" min="8710" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8960" min="8711" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8961" min="8961" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8961" min="8961" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8962" min="8962" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8963" min="8963" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8964" min="8964" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8965" min="8965" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8966" min="8966" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9216" min="8967" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9217" min="9217" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9217" min="9217" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9218" min="9218" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9219" min="9219" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9220" min="9220" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9221" min="9221" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9222" min="9222" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9472" min="9223" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9473" min="9473" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9473" min="9473" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9474" min="9474" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9475" min="9475" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9476" min="9476" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9477" min="9477" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9478" min="9478" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9728" min="9479" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9729" min="9729" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9729" min="9729" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9730" min="9730" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9731" min="9731" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9732" min="9732" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9733" min="9733" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9734" min="9734" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9984" min="9735" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9985" min="9985" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9985" min="9985" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9986" min="9986" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9987" min="9987" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9988" min="9988" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9989" min="9989" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9990" min="9990" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10240" min="9991" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10241" min="10241" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10241" min="10241" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10242" min="10242" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10243" min="10243" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10244" min="10244" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10245" min="10245" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10246" min="10246" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10496" min="10247" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10497" min="10497" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10497" min="10497" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10498" min="10498" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10499" min="10499" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10500" min="10500" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10501" min="10501" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10502" min="10502" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10752" min="10503" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10753" min="10753" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10753" min="10753" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10754" min="10754" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10755" min="10755" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10756" min="10756" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10757" min="10757" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10758" min="10758" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11008" min="10759" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11009" min="11009" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11009" min="11009" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11010" min="11010" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11011" min="11011" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11012" min="11012" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11013" min="11013" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11014" min="11014" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11264" min="11015" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11265" min="11265" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11265" min="11265" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11266" min="11266" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11267" min="11267" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11268" min="11268" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11269" min="11269" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11270" min="11270" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11520" min="11271" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11521" min="11521" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11521" min="11521" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11522" min="11522" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11523" min="11523" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11524" min="11524" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11525" min="11525" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11526" min="11526" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11776" min="11527" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11777" min="11777" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11777" min="11777" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11778" min="11778" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11779" min="11779" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11780" min="11780" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11781" min="11781" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11782" min="11782" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12032" min="11783" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12033" min="12033" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12033" min="12033" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12034" min="12034" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12035" min="12035" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12036" min="12036" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12037" min="12037" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12038" min="12038" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12288" min="12039" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12289" min="12289" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12289" min="12289" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12290" min="12290" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12291" min="12291" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12292" min="12292" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12293" min="12293" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12294" min="12294" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12544" min="12295" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12545" min="12545" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12545" min="12545" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12546" min="12546" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12547" min="12547" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12548" min="12548" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12549" min="12549" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12550" min="12550" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="12800" min="12551" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12801" min="12801" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12801" min="12801" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12802" min="12802" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12803" min="12803" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12804" min="12804" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12805" min="12805" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12806" min="12806" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13056" min="12807" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13057" min="13057" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13057" min="13057" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13058" min="13058" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13059" min="13059" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13060" min="13060" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13061" min="13061" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13062" min="13062" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13312" min="13063" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13313" min="13313" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13313" min="13313" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13314" min="13314" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13315" min="13315" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13316" min="13316" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13317" min="13317" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13318" min="13318" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13568" min="13319" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13569" min="13569" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13569" min="13569" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13570" min="13570" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13571" min="13571" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13572" min="13572" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13573" min="13573" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13574" min="13574" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13824" min="13575" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13825" min="13825" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13825" min="13825" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13826" min="13826" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13827" min="13827" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13828" min="13828" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13829" min="13829" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13830" min="13830" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14080" min="13831" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14081" min="14081" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14081" min="14081" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14082" min="14082" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14083" min="14083" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14084" min="14084" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14085" min="14085" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14086" min="14086" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14336" min="14087" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14337" min="14337" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14337" min="14337" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14338" min="14338" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14339" min="14339" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14340" min="14340" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14341" min="14341" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14342" min="14342" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14592" min="14343" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14593" min="14593" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14593" min="14593" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14594" min="14594" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14595" min="14595" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14596" min="14596" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14597" min="14597" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14598" min="14598" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="14848" min="14599" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14849" min="14849" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14849" min="14849" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14850" min="14850" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14851" min="14851" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14852" min="14852" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14853" min="14853" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14854" min="14854" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15104" min="14855" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15105" min="15105" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15105" min="15105" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15106" min="15106" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15107" min="15107" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15108" min="15108" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15109" min="15109" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15110" min="15110" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15360" min="15111" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15361" min="15361" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15361" min="15361" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15362" min="15362" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15363" min="15363" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15364" min="15364" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15365" min="15365" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15366" min="15366" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15616" min="15367" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15617" min="15617" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15617" min="15617" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15618" min="15618" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15619" min="15619" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15620" min="15620" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15621" min="15621" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15622" min="15622" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15872" min="15623" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15873" min="15873" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15873" min="15873" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15874" min="15874" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15875" min="15875" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15876" min="15876" style="2" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15877" min="15877" style="2" width="38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15878" min="15878" style="2" width="48.12"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16128" min="15879" style="2" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16129" min="16129" style="2" width="28.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16129" min="16129" style="2" width="28.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16130" min="16130" style="2" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16131" min="16131" style="2" width="14.38"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16132" min="16132" style="2" width="8"/>
@@ -3473,13 +3472,13 @@
         <v>55</v>
       </c>
       <c r="D18" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="62" t="s">
+      <c r="F18" s="63" t="s">
         <v>57</v>
-      </c>
-      <c r="F18" s="63" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3487,16 +3486,16 @@
         <v>11</v>
       </c>
       <c r="C19" s="60" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="62" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="62" t="s">
+      <c r="F19" s="63" t="s">
         <v>60</v>
-      </c>
-      <c r="F19" s="63" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3504,16 +3503,16 @@
         <v>12</v>
       </c>
       <c r="C20" s="60" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="62" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="62" t="s">
+      <c r="F20" s="63" t="s">
         <v>63</v>
-      </c>
-      <c r="F20" s="63" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3521,16 +3520,16 @@
         <v>13</v>
       </c>
       <c r="C21" s="60" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="62" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="62" t="s">
+      <c r="F21" s="63" t="s">
         <v>66</v>
-      </c>
-      <c r="F21" s="63" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3538,16 +3537,16 @@
         <v>14</v>
       </c>
       <c r="C22" s="60" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="62" t="s">
         <v>68</v>
       </c>
-      <c r="D22" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="62" t="s">
+      <c r="F22" s="63" t="s">
         <v>69</v>
-      </c>
-      <c r="F22" s="63" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3555,16 +3554,16 @@
         <v>15</v>
       </c>
       <c r="C23" s="60" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="62" t="s">
+      <c r="F23" s="63" t="s">
         <v>72</v>
-      </c>
-      <c r="F23" s="63" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3572,16 +3571,16 @@
         <v>16</v>
       </c>
       <c r="C24" s="60" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="E24" s="62" t="s">
+      <c r="F24" s="63" t="s">
         <v>75</v>
-      </c>
-      <c r="F24" s="63" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3589,16 +3588,16 @@
         <v>17</v>
       </c>
       <c r="C25" s="60" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D25" s="61" t="s">
         <v>31</v>
       </c>
       <c r="E25" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="63" t="s">
         <v>78</v>
-      </c>
-      <c r="F25" s="63" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3606,16 +3605,16 @@
         <v>18</v>
       </c>
       <c r="C26" s="60" t="s">
+        <v>79</v>
+      </c>
+      <c r="D26" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="E26" s="62" t="s">
+      <c r="F26" s="63" t="s">
         <v>81</v>
-      </c>
-      <c r="F26" s="63" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3623,16 +3622,16 @@
         <v>19</v>
       </c>
       <c r="C27" s="60" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D27" s="61" t="s">
         <v>31</v>
       </c>
       <c r="E27" s="62" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" s="63" t="s">
         <v>84</v>
-      </c>
-      <c r="F27" s="63" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3640,16 +3639,16 @@
         <v>20</v>
       </c>
       <c r="C28" s="60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D28" s="61" t="s">
         <v>31</v>
       </c>
       <c r="E28" s="62" t="s">
+        <v>86</v>
+      </c>
+      <c r="F28" s="63" t="s">
         <v>87</v>
-      </c>
-      <c r="F28" s="63" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3657,16 +3656,16 @@
         <v>21</v>
       </c>
       <c r="C29" s="60" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="D29" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" s="62" t="s">
+      <c r="F29" s="63" t="s">
         <v>90</v>
-      </c>
-      <c r="F29" s="63" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3674,10 +3673,10 @@
         <v>22</v>
       </c>
       <c r="C30" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="D30" s="61" t="s">
         <v>92</v>
-      </c>
-      <c r="D30" s="61" t="s">
-        <v>56</v>
       </c>
       <c r="E30" s="62" t="s">
         <v>93</v>
@@ -3694,7 +3693,7 @@
         <v>95</v>
       </c>
       <c r="D31" s="61" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="E31" s="62" t="s">
         <v>96</v>
@@ -3711,7 +3710,7 @@
         <v>98</v>
       </c>
       <c r="D32" s="61" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="E32" s="62" t="s">
         <v>99</v>
@@ -3728,7 +3727,7 @@
         <v>101</v>
       </c>
       <c r="D33" s="61" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="E33" s="62" t="s">
         <v>102</v>
@@ -3745,7 +3744,7 @@
         <v>104</v>
       </c>
       <c r="D34" s="61" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="E34" s="62" t="s">
         <v>105</v>
@@ -3762,7 +3761,7 @@
         <v>107</v>
       </c>
       <c r="D35" s="61" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="E35" s="62" t="s">
         <v>108</v>
@@ -3958,24 +3957,24 @@
         <v>120</v>
       </c>
       <c r="D11" s="86" t="n">
-        <f aca="false">COUNTIF('Feature 1'!$F$12:$F$23,"Passed")</f>
-        <v>12</v>
+        <f aca="false">COUNTIF('Feature 1'!$F$12:$F$32,"Passed")</f>
+        <v>21</v>
       </c>
       <c r="E11" s="86" t="n">
-        <f aca="false">COUNTIF('Feature 1'!$F$12:$F$23,"Failed")</f>
+        <f aca="false">COUNTIF('Feature 1'!$F$12:$F$32,"Failed")</f>
         <v>0</v>
       </c>
       <c r="F11" s="86" t="n">
-        <f aca="false">COUNTIF('Feature 1'!$F$12:$F$23,"Pending")</f>
+        <f aca="false">COUNTIF('Feature 1'!$F$12:$F$32,"Pending")</f>
         <v>0</v>
       </c>
       <c r="G11" s="86" t="n">
-        <f aca="false">COUNTIF('Feature 1'!$F$12:$F$23,"Blocked")</f>
+        <f aca="false">COUNTIF('Feature 1'!$F$12:$F$32,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="H11" s="87" t="n">
         <f aca="false">SUM(D11:G11)</f>
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3987,24 +3986,24 @@
         <v>121</v>
       </c>
       <c r="D12" s="86" t="n">
-        <f aca="false">COUNTIF('Feature 2'!$F$12:$F$26,"Passed")</f>
+        <f aca="false">COUNTIF('Feature 2'!$F$12:$F$17,"Passed")</f>
         <v>0</v>
       </c>
       <c r="E12" s="86" t="n">
-        <f aca="false">COUNTIF('Feature 2'!$F$12:$F$26,"Failed")</f>
+        <f aca="false">COUNTIF('Feature 2'!$F$12:$F$17,"Failed")</f>
         <v>0</v>
       </c>
       <c r="F12" s="86" t="n">
-        <f aca="false">COUNTIF('Feature 2'!$F$12:$F$26,"Pending")</f>
-        <v>15</v>
+        <f aca="false">COUNTIF('Feature 2'!$F$12:$F$17,"Pending")</f>
+        <v>6</v>
       </c>
       <c r="G12" s="86" t="n">
-        <f aca="false">COUNTIF('Feature 2'!$F$12:$F$26,"Blocked")</f>
+        <f aca="false">COUNTIF('Feature 2'!$F$12:$F$17,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="H12" s="86" t="n">
         <f aca="false">SUM(D12:G12)</f>
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4025,7 +4024,7 @@
       </c>
       <c r="D14" s="92" t="n">
         <f aca="false">SUM(D11:D12)</f>
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E14" s="92" t="n">
         <f aca="false">SUM(E11:E12)</f>
@@ -4033,7 +4032,7 @@
       </c>
       <c r="F14" s="92" t="n">
         <f aca="false">SUM(F11:F12)</f>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G14" s="92" t="n">
         <f aca="false">SUM(G11:G12)</f>
@@ -4063,7 +4062,7 @@
       <c r="D16" s="50"/>
       <c r="E16" s="98" t="n">
         <f aca="false">IFERROR((D14+E14)/(H14),0)</f>
-        <v>0.444444444444444</v>
+        <v>0.777777777777778</v>
       </c>
       <c r="F16" s="99"/>
       <c r="G16" s="50"/>
@@ -4123,7 +4122,7 @@
         <v>130</v>
       </c>
       <c r="C21" s="103" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D21" s="104" t="s">
         <v>131</v>
@@ -4138,7 +4137,7 @@
         <v>132</v>
       </c>
       <c r="C22" s="103" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D22" s="104" t="s">
         <v>133</v>
@@ -4183,7 +4182,7 @@
         <v>137</v>
       </c>
       <c r="C25" s="103" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D25" s="104" t="s">
         <v>138</v>
@@ -4213,10 +4212,10 @@
         <v>141</v>
       </c>
       <c r="C27" s="105" t="n">
-        <v>0.53125</v>
+        <v>1</v>
       </c>
       <c r="D27" s="104" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E27" s="104"/>
       <c r="F27" s="104"/>
@@ -4225,13 +4224,13 @@
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="102" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C28" s="103" t="n">
         <v>160</v>
       </c>
       <c r="D28" s="104" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E28" s="104"/>
       <c r="F28" s="104"/>
@@ -4240,13 +4239,13 @@
     </row>
     <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="102" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C29" s="103" t="n">
         <v>12</v>
       </c>
       <c r="D29" s="104" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E29" s="104"/>
       <c r="F29" s="104"/>
@@ -4291,7 +4290,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="12.75" customHeight="false" zeroHeight="false" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="38" width="18"/>
@@ -4307,15 +4306,15 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="38" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="14" min="13" style="38" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="38" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="38" width="10.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="106" width="8.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="38" width="10.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="106" width="8.14"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="18" style="38" width="7.63"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="19" style="38" width="9"/>
   </cols>
   <sheetData>
     <row r="1" s="114" customFormat="true" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="107" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B1" s="108" t="s">
         <v>120</v>
@@ -4341,10 +4340,10 @@
     </row>
     <row r="2" s="114" customFormat="true" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="115" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" s="116" t="s">
         <v>148</v>
-      </c>
-      <c r="B2" s="116" t="s">
-        <v>149</v>
       </c>
       <c r="C2" s="116"/>
       <c r="D2" s="116"/>
@@ -4370,8 +4369,8 @@
         <v>119</v>
       </c>
       <c r="B3" s="116" t="n">
-        <f aca="false">COUNTA(A12:A23)</f>
-        <v>12</v>
+        <f aca="false">COUNTA(A12:A32)</f>
+        <v>21</v>
       </c>
       <c r="C3" s="116"/>
       <c r="D3" s="116"/>
@@ -4394,7 +4393,7 @@
     </row>
     <row r="4" s="114" customFormat="true" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="117" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B4" s="118" t="s">
         <v>115</v>
@@ -4406,7 +4405,7 @@
         <v>117</v>
       </c>
       <c r="E4" s="119" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F4" s="120"/>
       <c r="G4" s="120"/>
@@ -4421,27 +4420,27 @@
       <c r="P4" s="121"/>
       <c r="Q4" s="122"/>
       <c r="R4" s="113" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" s="114" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="117" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B5" s="123" t="n">
-        <f aca="false">COUNTIF($F$12:$F$23,"Passed")</f>
-        <v>12</v>
+        <f aca="false">COUNTIF($F$12:$F$32,"Passed")</f>
+        <v>21</v>
       </c>
       <c r="C5" s="123" t="n">
-        <f aca="false">COUNTIF($F$12:$F$23,"Failed")</f>
+        <f aca="false">COUNTIF($F$12:$F$32,"Failed")</f>
         <v>0</v>
       </c>
       <c r="D5" s="123" t="n">
-        <f aca="false">COUNTIF($F$12:$F$23,"Pending")</f>
+        <f aca="false">COUNTIF($F$12:$F$32,"Pending")</f>
         <v>0</v>
       </c>
       <c r="E5" s="124" t="n">
-        <f aca="false">COUNTIF($F$12:$F$23,"Blocked")</f>
+        <f aca="false">COUNTIF($F$12:$F$32,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F5" s="125"/>
@@ -4459,11 +4458,11 @@
     </row>
     <row r="6" s="114" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="117" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B6" s="123" t="n">
         <f aca="false">COUNTIF($F10:$F996,B4)</f>
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C6" s="123" t="n">
         <f aca="false">COUNTIF($F10:$F996,C4)</f>
@@ -4492,11 +4491,11 @@
     </row>
     <row r="7" s="114" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="126" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B7" s="127" t="n">
         <f aca="false">COUNTIF($F10:$F996,B4)</f>
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C7" s="127" t="n">
         <f aca="false">COUNTIF($F10:$F996,C4)</f>
@@ -4563,46 +4562,46 @@
     </row>
     <row r="10" s="114" customFormat="true" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="129" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="129" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="129" t="s">
+      <c r="C10" s="129" t="s">
         <v>157</v>
       </c>
-      <c r="C10" s="129" t="s">
+      <c r="D10" s="129" t="s">
         <v>158</v>
-      </c>
-      <c r="D10" s="129" t="s">
-        <v>159</v>
       </c>
       <c r="E10" s="129" t="s">
         <v>29</v>
       </c>
       <c r="F10" s="129" t="s">
+        <v>152</v>
+      </c>
+      <c r="G10" s="129" t="s">
+        <v>159</v>
+      </c>
+      <c r="H10" s="129" t="s">
+        <v>160</v>
+      </c>
+      <c r="I10" s="129" t="s">
         <v>153</v>
       </c>
-      <c r="G10" s="129" t="s">
+      <c r="J10" s="129" t="s">
+        <v>159</v>
+      </c>
+      <c r="K10" s="129" t="s">
         <v>160</v>
       </c>
-      <c r="H10" s="129" t="s">
-        <v>161</v>
-      </c>
-      <c r="I10" s="129" t="s">
+      <c r="L10" s="129" t="s">
         <v>154</v>
       </c>
-      <c r="J10" s="129" t="s">
+      <c r="M10" s="129" t="s">
+        <v>159</v>
+      </c>
+      <c r="N10" s="129" t="s">
         <v>160</v>
-      </c>
-      <c r="K10" s="129" t="s">
-        <v>161</v>
-      </c>
-      <c r="L10" s="129" t="s">
-        <v>155</v>
-      </c>
-      <c r="M10" s="129" t="s">
-        <v>160</v>
-      </c>
-      <c r="N10" s="129" t="s">
-        <v>161</v>
       </c>
       <c r="O10" s="129" t="s">
         <v>112</v>
@@ -4611,7 +4610,7 @@
     </row>
     <row r="11" s="114" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="131" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="133"/>
@@ -4631,16 +4630,16 @@
     </row>
     <row r="12" s="139" customFormat="true" ht="109.5" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A12" s="136" t="s">
+        <v>162</v>
+      </c>
+      <c r="B12" s="137" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="137" t="s">
+      <c r="C12" s="137" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="137" t="s">
+      <c r="D12" s="46" t="s">
         <v>165</v>
-      </c>
-      <c r="D12" s="46" t="s">
-        <v>166</v>
       </c>
       <c r="E12" s="46" t="s">
         <v>33</v>
@@ -4649,38 +4648,38 @@
         <v>115</v>
       </c>
       <c r="G12" s="136" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H12" s="136" t="s">
         <v>4</v>
       </c>
       <c r="I12" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J12" s="116"/>
       <c r="K12" s="116"/>
       <c r="L12" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M12" s="116"/>
       <c r="N12" s="116"/>
       <c r="O12" s="138" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q12" s="140"/>
     </row>
     <row r="13" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A13" s="136" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" s="116" t="s">
         <v>169</v>
       </c>
-      <c r="B13" s="116" t="s">
+      <c r="C13" s="116" t="s">
         <v>170</v>
       </c>
-      <c r="C13" s="116" t="s">
+      <c r="D13" s="141" t="s">
         <v>171</v>
-      </c>
-      <c r="D13" s="141" t="s">
-        <v>172</v>
       </c>
       <c r="E13" s="141" t="s">
         <v>35</v>
@@ -4689,38 +4688,38 @@
         <v>115</v>
       </c>
       <c r="G13" s="136" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H13" s="136" t="s">
         <v>4</v>
       </c>
       <c r="I13" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J13" s="116"/>
       <c r="K13" s="116"/>
       <c r="L13" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M13" s="116"/>
       <c r="N13" s="116"/>
       <c r="O13" s="138" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q13" s="140"/>
     </row>
     <row r="14" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A14" s="136" t="s">
+        <v>173</v>
+      </c>
+      <c r="B14" s="116" t="s">
         <v>174</v>
       </c>
-      <c r="B14" s="116" t="s">
+      <c r="C14" s="116" t="s">
         <v>175</v>
       </c>
-      <c r="C14" s="116" t="s">
+      <c r="D14" s="141" t="s">
         <v>176</v>
-      </c>
-      <c r="D14" s="141" t="s">
-        <v>177</v>
       </c>
       <c r="E14" s="141" t="s">
         <v>37</v>
@@ -4729,38 +4728,38 @@
         <v>115</v>
       </c>
       <c r="G14" s="136" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H14" s="136" t="s">
         <v>4</v>
       </c>
       <c r="I14" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J14" s="116"/>
       <c r="K14" s="116"/>
       <c r="L14" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M14" s="116"/>
       <c r="N14" s="116"/>
       <c r="O14" s="138" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q14" s="140"/>
     </row>
     <row r="15" s="114" customFormat="true" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="142" t="s">
+        <v>178</v>
+      </c>
+      <c r="B15" s="143" t="s">
         <v>179</v>
       </c>
-      <c r="B15" s="143" t="s">
+      <c r="C15" s="144" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="144" t="s">
+      <c r="D15" s="144" t="s">
         <v>181</v>
-      </c>
-      <c r="D15" s="144" t="s">
-        <v>182</v>
       </c>
       <c r="E15" s="144" t="s">
         <v>40</v>
@@ -4769,38 +4768,38 @@
         <v>115</v>
       </c>
       <c r="G15" s="145" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H15" s="145" t="s">
         <v>4</v>
       </c>
       <c r="I15" s="144" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J15" s="144"/>
       <c r="K15" s="144"/>
       <c r="L15" s="144" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M15" s="144"/>
       <c r="N15" s="144"/>
       <c r="O15" s="146" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q15" s="135"/>
     </row>
     <row r="16" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A16" s="136" t="s">
+        <v>183</v>
+      </c>
+      <c r="B16" s="116" t="s">
         <v>184</v>
       </c>
-      <c r="B16" s="116" t="s">
+      <c r="C16" s="116" t="s">
         <v>185</v>
       </c>
-      <c r="C16" s="116" t="s">
+      <c r="D16" s="116" t="s">
         <v>186</v>
-      </c>
-      <c r="D16" s="116" t="s">
-        <v>187</v>
       </c>
       <c r="E16" s="116" t="s">
         <v>42</v>
@@ -4809,38 +4808,38 @@
         <v>115</v>
       </c>
       <c r="G16" s="136" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H16" s="136" t="s">
         <v>4</v>
       </c>
       <c r="I16" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J16" s="116"/>
       <c r="K16" s="116"/>
       <c r="L16" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M16" s="116"/>
       <c r="N16" s="116"/>
       <c r="O16" s="138" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q16" s="140"/>
     </row>
     <row r="17" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A17" s="136" t="s">
+        <v>188</v>
+      </c>
+      <c r="B17" s="116" t="s">
         <v>189</v>
       </c>
-      <c r="B17" s="116" t="s">
+      <c r="C17" s="116" t="s">
         <v>190</v>
       </c>
-      <c r="C17" s="116" t="s">
+      <c r="D17" s="116" t="s">
         <v>191</v>
-      </c>
-      <c r="D17" s="116" t="s">
-        <v>192</v>
       </c>
       <c r="E17" s="116" t="s">
         <v>45</v>
@@ -4849,38 +4848,38 @@
         <v>115</v>
       </c>
       <c r="G17" s="147" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H17" s="147" t="s">
         <v>4</v>
       </c>
       <c r="I17" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J17" s="138"/>
       <c r="K17" s="138"/>
       <c r="L17" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M17" s="138"/>
       <c r="N17" s="138"/>
       <c r="O17" s="138" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q17" s="148"/>
     </row>
     <row r="18" s="114" customFormat="true" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="142" t="s">
+        <v>194</v>
+      </c>
+      <c r="B18" s="143" t="s">
         <v>195</v>
       </c>
-      <c r="B18" s="143" t="s">
+      <c r="C18" s="144" t="s">
         <v>196</v>
       </c>
-      <c r="C18" s="144" t="s">
+      <c r="D18" s="144" t="s">
         <v>197</v>
-      </c>
-      <c r="D18" s="144" t="s">
-        <v>198</v>
       </c>
       <c r="E18" s="144" t="s">
         <v>48</v>
@@ -4889,38 +4888,38 @@
         <v>115</v>
       </c>
       <c r="G18" s="145" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H18" s="145" t="s">
         <v>4</v>
       </c>
       <c r="I18" s="144" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J18" s="144"/>
       <c r="K18" s="144"/>
       <c r="L18" s="144" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M18" s="144"/>
       <c r="N18" s="144"/>
       <c r="O18" s="146" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q18" s="135"/>
     </row>
     <row r="19" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A19" s="136" t="s">
+        <v>199</v>
+      </c>
+      <c r="B19" s="116" t="s">
         <v>200</v>
       </c>
-      <c r="B19" s="116" t="s">
+      <c r="C19" s="116" t="s">
         <v>201</v>
       </c>
-      <c r="C19" s="116" t="s">
+      <c r="D19" s="116" t="s">
         <v>202</v>
-      </c>
-      <c r="D19" s="116" t="s">
-        <v>203</v>
       </c>
       <c r="E19" s="116" t="s">
         <v>51</v>
@@ -4929,38 +4928,38 @@
         <v>115</v>
       </c>
       <c r="G19" s="136" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H19" s="136" t="s">
         <v>4</v>
       </c>
       <c r="I19" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J19" s="116"/>
       <c r="K19" s="116"/>
       <c r="L19" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M19" s="116"/>
       <c r="N19" s="116"/>
       <c r="O19" s="138" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q19" s="140"/>
     </row>
     <row r="20" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="136" t="s">
+        <v>204</v>
+      </c>
+      <c r="B20" s="137" t="s">
         <v>205</v>
       </c>
-      <c r="B20" s="137" t="s">
+      <c r="C20" s="137" t="s">
         <v>206</v>
       </c>
-      <c r="C20" s="137" t="s">
+      <c r="D20" s="46" t="s">
         <v>207</v>
-      </c>
-      <c r="D20" s="46" t="s">
-        <v>208</v>
       </c>
       <c r="E20" s="46" t="s">
         <v>54</v>
@@ -4969,58 +4968,58 @@
         <v>115</v>
       </c>
       <c r="G20" s="136" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H20" s="136" t="s">
         <v>4</v>
       </c>
       <c r="I20" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J20" s="116"/>
       <c r="K20" s="116"/>
       <c r="L20" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M20" s="116"/>
       <c r="N20" s="116"/>
       <c r="O20" s="138" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q20" s="140"/>
     </row>
     <row r="21" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="136" t="s">
+        <v>210</v>
+      </c>
+      <c r="B21" s="137" t="s">
         <v>211</v>
       </c>
-      <c r="B21" s="137" t="s">
+      <c r="C21" s="137" t="s">
         <v>212</v>
       </c>
-      <c r="C21" s="137" t="s">
+      <c r="D21" s="46" t="s">
         <v>213</v>
       </c>
-      <c r="D21" s="46" t="s">
-        <v>214</v>
-      </c>
       <c r="E21" s="46" t="s">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="F21" s="136" t="s">
         <v>115</v>
       </c>
       <c r="G21" s="136" t="s">
+        <v>214</v>
+      </c>
+      <c r="H21" s="136" t="s">
         <v>215</v>
       </c>
-      <c r="H21" s="136" t="s">
-        <v>4</v>
-      </c>
       <c r="I21" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J21" s="116"/>
       <c r="K21" s="116"/>
       <c r="L21" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M21" s="116"/>
       <c r="N21" s="116"/>
@@ -5043,71 +5042,431 @@
         <v>220</v>
       </c>
       <c r="E22" s="46" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="F22" s="136" t="s">
         <v>115</v>
       </c>
       <c r="G22" s="136" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="H22" s="136" t="s">
-        <v>4</v>
+        <v>215</v>
       </c>
       <c r="I22" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J22" s="116"/>
       <c r="K22" s="116"/>
       <c r="L22" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M22" s="116"/>
       <c r="N22" s="116"/>
       <c r="O22" s="138" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q22" s="140"/>
     </row>
     <row r="23" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="136" t="s">
+        <v>222</v>
+      </c>
+      <c r="B23" s="137" t="s">
         <v>223</v>
       </c>
-      <c r="B23" s="137" t="s">
+      <c r="C23" s="137" t="s">
         <v>224</v>
       </c>
-      <c r="C23" s="137" t="s">
+      <c r="D23" s="46" t="s">
         <v>225</v>
       </c>
-      <c r="D23" s="46" t="s">
-        <v>226</v>
-      </c>
       <c r="E23" s="46" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="F23" s="136" t="s">
         <v>115</v>
       </c>
       <c r="G23" s="136" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="H23" s="136" t="s">
-        <v>4</v>
+        <v>215</v>
       </c>
       <c r="I23" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J23" s="116"/>
       <c r="K23" s="116"/>
       <c r="L23" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M23" s="116"/>
       <c r="N23" s="116"/>
       <c r="O23" s="138" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q23" s="140"/>
+    </row>
+    <row r="24" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="136" t="s">
+        <v>227</v>
+      </c>
+      <c r="B24" s="137" t="s">
         <v>228</v>
       </c>
-      <c r="Q23" s="140"/>
+      <c r="C24" s="137" t="s">
+        <v>229</v>
+      </c>
+      <c r="D24" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="E24" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="136" t="s">
+        <v>115</v>
+      </c>
+      <c r="G24" s="136" t="s">
+        <v>214</v>
+      </c>
+      <c r="H24" s="136" t="s">
+        <v>215</v>
+      </c>
+      <c r="I24" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="J24" s="116"/>
+      <c r="K24" s="116"/>
+      <c r="L24" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="M24" s="116"/>
+      <c r="N24" s="116"/>
+      <c r="O24" s="138" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q24" s="140"/>
+    </row>
+    <row r="25" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="136" t="s">
+        <v>232</v>
+      </c>
+      <c r="B25" s="137" t="s">
+        <v>233</v>
+      </c>
+      <c r="C25" s="137" t="s">
+        <v>234</v>
+      </c>
+      <c r="D25" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="E25" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" s="136" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" s="136" t="s">
+        <v>214</v>
+      </c>
+      <c r="H25" s="136" t="s">
+        <v>215</v>
+      </c>
+      <c r="I25" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="J25" s="116"/>
+      <c r="K25" s="116"/>
+      <c r="L25" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="M25" s="116"/>
+      <c r="N25" s="116"/>
+      <c r="O25" s="138" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q25" s="140"/>
+    </row>
+    <row r="26" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="136" t="s">
+        <v>237</v>
+      </c>
+      <c r="B26" s="137" t="s">
+        <v>238</v>
+      </c>
+      <c r="C26" s="137" t="s">
+        <v>239</v>
+      </c>
+      <c r="D26" s="46" t="s">
+        <v>240</v>
+      </c>
+      <c r="E26" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="136" t="s">
+        <v>115</v>
+      </c>
+      <c r="G26" s="136" t="s">
+        <v>214</v>
+      </c>
+      <c r="H26" s="136" t="s">
+        <v>215</v>
+      </c>
+      <c r="I26" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="J26" s="116"/>
+      <c r="K26" s="116"/>
+      <c r="L26" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="M26" s="116"/>
+      <c r="N26" s="116"/>
+      <c r="O26" s="138" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q26" s="140"/>
+    </row>
+    <row r="27" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="136" t="s">
+        <v>242</v>
+      </c>
+      <c r="B27" s="137" t="s">
+        <v>243</v>
+      </c>
+      <c r="C27" s="137" t="s">
+        <v>244</v>
+      </c>
+      <c r="D27" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="E27" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="F27" s="136" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" s="136" t="s">
+        <v>214</v>
+      </c>
+      <c r="H27" s="136" t="s">
+        <v>215</v>
+      </c>
+      <c r="I27" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="J27" s="116"/>
+      <c r="K27" s="116"/>
+      <c r="L27" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="M27" s="116"/>
+      <c r="N27" s="116"/>
+      <c r="O27" s="138" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q27" s="140"/>
+    </row>
+    <row r="28" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="136" t="s">
+        <v>247</v>
+      </c>
+      <c r="B28" s="137" t="s">
+        <v>248</v>
+      </c>
+      <c r="C28" s="137" t="s">
+        <v>249</v>
+      </c>
+      <c r="D28" s="46" t="s">
+        <v>250</v>
+      </c>
+      <c r="E28" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" s="136" t="s">
+        <v>115</v>
+      </c>
+      <c r="G28" s="136" t="s">
+        <v>251</v>
+      </c>
+      <c r="H28" s="136" t="s">
+        <v>4</v>
+      </c>
+      <c r="I28" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="J28" s="116"/>
+      <c r="K28" s="116"/>
+      <c r="L28" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="M28" s="116"/>
+      <c r="N28" s="116"/>
+      <c r="O28" s="138" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q28" s="140"/>
+    </row>
+    <row r="29" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="136" t="s">
+        <v>253</v>
+      </c>
+      <c r="B29" s="137" t="s">
+        <v>254</v>
+      </c>
+      <c r="C29" s="137" t="s">
+        <v>255</v>
+      </c>
+      <c r="D29" s="46" t="s">
+        <v>256</v>
+      </c>
+      <c r="E29" s="46" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="136" t="s">
+        <v>115</v>
+      </c>
+      <c r="G29" s="136" t="s">
+        <v>214</v>
+      </c>
+      <c r="H29" s="136" t="s">
+        <v>215</v>
+      </c>
+      <c r="I29" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="J29" s="116"/>
+      <c r="K29" s="116"/>
+      <c r="L29" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="M29" s="116"/>
+      <c r="N29" s="116"/>
+      <c r="O29" s="138" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q29" s="140"/>
+    </row>
+    <row r="30" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="136" t="s">
+        <v>258</v>
+      </c>
+      <c r="B30" s="137" t="s">
+        <v>259</v>
+      </c>
+      <c r="C30" s="137" t="s">
+        <v>260</v>
+      </c>
+      <c r="D30" s="46" t="s">
+        <v>261</v>
+      </c>
+      <c r="E30" s="46" t="s">
+        <v>84</v>
+      </c>
+      <c r="F30" s="136" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" s="136" t="s">
+        <v>262</v>
+      </c>
+      <c r="H30" s="136" t="s">
+        <v>4</v>
+      </c>
+      <c r="I30" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="J30" s="116"/>
+      <c r="K30" s="116"/>
+      <c r="L30" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="M30" s="116"/>
+      <c r="N30" s="116"/>
+      <c r="O30" s="138" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q30" s="140"/>
+    </row>
+    <row r="31" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="136" t="s">
+        <v>264</v>
+      </c>
+      <c r="B31" s="137" t="s">
+        <v>265</v>
+      </c>
+      <c r="C31" s="137" t="s">
+        <v>266</v>
+      </c>
+      <c r="D31" s="46" t="s">
+        <v>267</v>
+      </c>
+      <c r="E31" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31" s="136" t="s">
+        <v>115</v>
+      </c>
+      <c r="G31" s="136" t="s">
+        <v>268</v>
+      </c>
+      <c r="H31" s="136" t="s">
+        <v>4</v>
+      </c>
+      <c r="I31" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="J31" s="116"/>
+      <c r="K31" s="116"/>
+      <c r="L31" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="M31" s="116"/>
+      <c r="N31" s="116"/>
+      <c r="O31" s="138" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q31" s="140"/>
+    </row>
+    <row r="32" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="136" t="s">
+        <v>270</v>
+      </c>
+      <c r="B32" s="137" t="s">
+        <v>271</v>
+      </c>
+      <c r="C32" s="137" t="s">
+        <v>272</v>
+      </c>
+      <c r="D32" s="46" t="s">
+        <v>273</v>
+      </c>
+      <c r="E32" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="F32" s="136" t="s">
+        <v>115</v>
+      </c>
+      <c r="G32" s="136" t="s">
+        <v>214</v>
+      </c>
+      <c r="H32" s="136" t="s">
+        <v>215</v>
+      </c>
+      <c r="I32" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="J32" s="116"/>
+      <c r="K32" s="116"/>
+      <c r="L32" s="116" t="s">
+        <v>151</v>
+      </c>
+      <c r="M32" s="116"/>
+      <c r="N32" s="116"/>
+      <c r="O32" s="138" t="s">
+        <v>274</v>
+      </c>
+      <c r="Q32" s="140"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5158,8 +5517,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="38" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="1" max="14" min="13" style="38" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="38" width="62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="38" width="10.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="106" width="8.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="38" width="10.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="106" width="8.14"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="18" style="38" width="7.63"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="19" style="38" width="9"/>
   </cols>
@@ -5167,7 +5526,7 @@
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" s="114" customFormat="true" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="107" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B2" s="108" t="s">
         <v>121</v>
@@ -5193,10 +5552,10 @@
     </row>
     <row r="3" s="114" customFormat="true" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="115" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B3" s="116" t="s">
-        <v>229</v>
+        <v>275</v>
       </c>
       <c r="C3" s="116"/>
       <c r="D3" s="116"/>
@@ -5222,8 +5581,8 @@
         <v>119</v>
       </c>
       <c r="B4" s="116" t="n">
-        <f aca="false">COUNTA(A12:A26)</f>
-        <v>15</v>
+        <f aca="false">COUNTA(A12:A17)</f>
+        <v>6</v>
       </c>
       <c r="C4" s="116"/>
       <c r="D4" s="116"/>
@@ -5246,7 +5605,7 @@
     </row>
     <row r="5" s="114" customFormat="true" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="117" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B5" s="118" t="s">
         <v>115</v>
@@ -5258,7 +5617,7 @@
         <v>117</v>
       </c>
       <c r="E5" s="119" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F5" s="120"/>
       <c r="G5" s="120"/>
@@ -5273,27 +5632,27 @@
       <c r="P5" s="121"/>
       <c r="Q5" s="122"/>
       <c r="R5" s="113" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" s="114" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="117" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B6" s="123" t="n">
-        <f aca="false">COUNTIF($F$12:$F$26,"Passed")</f>
+        <f aca="false">COUNTIF($F$12:$F$17,"Passed")</f>
         <v>0</v>
       </c>
       <c r="C6" s="123" t="n">
-        <f aca="false">COUNTIF($F$12:$F$26,"Failed")</f>
+        <f aca="false">COUNTIF($F$12:$F$17,"Failed")</f>
         <v>0</v>
       </c>
       <c r="D6" s="123" t="n">
-        <f aca="false">COUNTIF($F$12:$F$26,"Pending")</f>
-        <v>15</v>
+        <f aca="false">COUNTIF($F$12:$F$17,"Pending")</f>
+        <v>6</v>
       </c>
       <c r="E6" s="124" t="n">
-        <f aca="false">COUNTIF($F$12:$F$26,"Blocked")</f>
+        <f aca="false">COUNTIF($F$12:$F$17,"Blocked")</f>
         <v>0</v>
       </c>
       <c r="F6" s="125"/>
@@ -5311,7 +5670,7 @@
     </row>
     <row r="7" s="114" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="117" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B7" s="123" t="n">
         <f aca="false">COUNTIF($F10:$F996,B5)</f>
@@ -5323,7 +5682,7 @@
       </c>
       <c r="D7" s="123" t="n">
         <f aca="false">COUNTIF($F10:$F996,D5)</f>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E7" s="124" t="n">
         <f aca="false">COUNTIF($F10:$F996,E5)</f>
@@ -5344,7 +5703,7 @@
     </row>
     <row r="8" s="114" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="126" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B8" s="127" t="n">
         <f aca="false">COUNTIF($F10:$F996,B5)</f>
@@ -5356,7 +5715,7 @@
       </c>
       <c r="D8" s="127" t="n">
         <f aca="false">COUNTIF($F10:$F996,D5)</f>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E8" s="128" t="n">
         <f aca="false">COUNTIF($F10:$F996,E5)</f>
@@ -5396,46 +5755,46 @@
     </row>
     <row r="10" s="114" customFormat="true" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="129" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="129" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="129" t="s">
+      <c r="C10" s="129" t="s">
         <v>157</v>
       </c>
-      <c r="C10" s="129" t="s">
+      <c r="D10" s="129" t="s">
         <v>158</v>
-      </c>
-      <c r="D10" s="129" t="s">
-        <v>159</v>
       </c>
       <c r="E10" s="129" t="s">
         <v>29</v>
       </c>
       <c r="F10" s="129" t="s">
+        <v>152</v>
+      </c>
+      <c r="G10" s="129" t="s">
+        <v>159</v>
+      </c>
+      <c r="H10" s="129" t="s">
+        <v>160</v>
+      </c>
+      <c r="I10" s="129" t="s">
         <v>153</v>
       </c>
-      <c r="G10" s="129" t="s">
+      <c r="J10" s="129" t="s">
+        <v>159</v>
+      </c>
+      <c r="K10" s="129" t="s">
         <v>160</v>
       </c>
-      <c r="H10" s="129" t="s">
-        <v>161</v>
-      </c>
-      <c r="I10" s="129" t="s">
+      <c r="L10" s="129" t="s">
         <v>154</v>
       </c>
-      <c r="J10" s="129" t="s">
+      <c r="M10" s="129" t="s">
+        <v>159</v>
+      </c>
+      <c r="N10" s="129" t="s">
         <v>160</v>
-      </c>
-      <c r="K10" s="129" t="s">
-        <v>161</v>
-      </c>
-      <c r="L10" s="129" t="s">
-        <v>155</v>
-      </c>
-      <c r="M10" s="129" t="s">
-        <v>160</v>
-      </c>
-      <c r="N10" s="129" t="s">
-        <v>161</v>
       </c>
       <c r="O10" s="129" t="s">
         <v>112</v>
@@ -5444,7 +5803,7 @@
     </row>
     <row r="11" s="114" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="131" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B11" s="132"/>
       <c r="C11" s="133"/>
@@ -5464,19 +5823,19 @@
     </row>
     <row r="12" s="139" customFormat="true" ht="109.5" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A12" s="136" t="s">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="B12" s="137" t="s">
-        <v>231</v>
+        <v>277</v>
       </c>
       <c r="C12" s="137" t="s">
-        <v>232</v>
+        <v>278</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="F12" s="136" t="s">
         <v>117</v>
@@ -5484,35 +5843,35 @@
       <c r="G12" s="136"/>
       <c r="H12" s="136"/>
       <c r="I12" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J12" s="116"/>
       <c r="K12" s="116"/>
       <c r="L12" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M12" s="116"/>
       <c r="N12" s="116"/>
       <c r="O12" s="138" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="Q12" s="140"/>
     </row>
     <row r="13" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A13" s="136" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="B13" s="116" t="s">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="C13" s="116" t="s">
-        <v>237</v>
+        <v>283</v>
       </c>
       <c r="D13" s="141" t="s">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="E13" s="141" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="F13" s="136" t="s">
         <v>117</v>
@@ -5520,35 +5879,35 @@
       <c r="G13" s="136"/>
       <c r="H13" s="136"/>
       <c r="I13" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J13" s="116"/>
       <c r="K13" s="116"/>
       <c r="L13" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M13" s="116"/>
       <c r="N13" s="116"/>
       <c r="O13" s="138" t="s">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="Q13" s="140"/>
     </row>
     <row r="14" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A14" s="136" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="B14" s="116" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C14" s="116" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="D14" s="141" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="E14" s="141" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="F14" s="136" t="s">
         <v>117</v>
@@ -5556,35 +5915,35 @@
       <c r="G14" s="136"/>
       <c r="H14" s="136"/>
       <c r="I14" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J14" s="116"/>
       <c r="K14" s="116"/>
       <c r="L14" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M14" s="116"/>
       <c r="N14" s="116"/>
       <c r="O14" s="138" t="s">
-        <v>244</v>
+        <v>289</v>
       </c>
       <c r="Q14" s="140"/>
     </row>
     <row r="15" s="114" customFormat="true" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="142" t="s">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="B15" s="143" t="s">
-        <v>246</v>
+        <v>291</v>
       </c>
       <c r="C15" s="144" t="s">
-        <v>247</v>
+        <v>292</v>
       </c>
       <c r="D15" s="144" t="s">
-        <v>248</v>
+        <v>293</v>
       </c>
       <c r="E15" s="144" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="F15" s="145" t="s">
         <v>117</v>
@@ -5592,35 +5951,35 @@
       <c r="G15" s="145"/>
       <c r="H15" s="145"/>
       <c r="I15" s="144" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J15" s="144"/>
       <c r="K15" s="144"/>
       <c r="L15" s="144" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M15" s="144"/>
       <c r="N15" s="144"/>
       <c r="O15" s="146" t="s">
-        <v>249</v>
+        <v>294</v>
       </c>
       <c r="Q15" s="135"/>
     </row>
     <row r="16" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A16" s="136" t="s">
-        <v>250</v>
+        <v>295</v>
       </c>
       <c r="B16" s="116" t="s">
-        <v>251</v>
+        <v>296</v>
       </c>
       <c r="C16" s="116" t="s">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="D16" s="116" t="s">
-        <v>253</v>
+        <v>298</v>
       </c>
       <c r="E16" s="116" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="F16" s="136" t="s">
         <v>117</v>
@@ -5628,35 +5987,35 @@
       <c r="G16" s="136"/>
       <c r="H16" s="136"/>
       <c r="I16" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J16" s="116"/>
       <c r="K16" s="116"/>
       <c r="L16" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M16" s="116"/>
       <c r="N16" s="116"/>
       <c r="O16" s="138" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="Q16" s="140"/>
     </row>
     <row r="17" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="1" collapsed="false">
       <c r="A17" s="136" t="s">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="B17" s="116" t="s">
-        <v>256</v>
+        <v>301</v>
       </c>
       <c r="C17" s="116" t="s">
-        <v>257</v>
+        <v>302</v>
       </c>
       <c r="D17" s="116" t="s">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="E17" s="116" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="F17" s="136" t="s">
         <v>117</v>
@@ -5664,342 +6023,31 @@
       <c r="G17" s="147"/>
       <c r="H17" s="147"/>
       <c r="I17" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J17" s="138"/>
       <c r="K17" s="138"/>
       <c r="L17" s="116" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M17" s="138"/>
       <c r="N17" s="138"/>
       <c r="O17" s="138" t="s">
-        <v>259</v>
+        <v>304</v>
       </c>
       <c r="Q17" s="148"/>
     </row>
     <row r="18" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="103" t="s">
-        <v>260</v>
-      </c>
-      <c r="B18" s="102" t="s">
-        <v>261</v>
-      </c>
-      <c r="C18" s="102" t="s">
-        <v>262</v>
-      </c>
-      <c r="D18" s="102" t="s">
-        <v>263</v>
-      </c>
-      <c r="E18" s="102" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" s="149" t="s">
-        <v>117</v>
-      </c>
-      <c r="G18" s="149"/>
-      <c r="H18" s="149"/>
-      <c r="I18" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="J18" s="102"/>
-      <c r="K18" s="102"/>
-      <c r="L18" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="M18" s="102"/>
-      <c r="N18" s="102"/>
-      <c r="O18" s="102" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="149" t="s">
-        <v>265</v>
-      </c>
-      <c r="B19" s="102" t="s">
-        <v>266</v>
-      </c>
-      <c r="C19" s="102" t="s">
-        <v>267</v>
-      </c>
-      <c r="D19" s="102" t="s">
-        <v>268</v>
-      </c>
-      <c r="E19" s="102" t="s">
-        <v>82</v>
-      </c>
-      <c r="F19" s="149" t="s">
-        <v>117</v>
-      </c>
-      <c r="G19" s="149"/>
-      <c r="H19" s="149"/>
-      <c r="I19" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="J19" s="102"/>
-      <c r="K19" s="102"/>
-      <c r="L19" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="M19" s="102"/>
-      <c r="N19" s="102"/>
-      <c r="O19" s="102" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="136" t="s">
-        <v>270</v>
-      </c>
-      <c r="B20" s="137" t="s">
-        <v>271</v>
-      </c>
-      <c r="C20" s="137" t="s">
-        <v>272</v>
-      </c>
-      <c r="D20" s="46" t="s">
-        <v>273</v>
-      </c>
-      <c r="E20" s="46" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" s="136" t="s">
-        <v>117</v>
-      </c>
-      <c r="G20" s="136"/>
-      <c r="H20" s="136"/>
-      <c r="I20" s="116" t="s">
-        <v>152</v>
-      </c>
-      <c r="J20" s="116"/>
-      <c r="K20" s="116"/>
-      <c r="L20" s="116" t="s">
-        <v>152</v>
-      </c>
-      <c r="M20" s="116"/>
-      <c r="N20" s="116"/>
-      <c r="O20" s="138" t="s">
-        <v>274</v>
-      </c>
-      <c r="Q20" s="140"/>
-    </row>
-    <row r="21" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="136" t="s">
-        <v>275</v>
-      </c>
-      <c r="B21" s="137" t="s">
-        <v>276</v>
-      </c>
-      <c r="C21" s="137" t="s">
-        <v>277</v>
-      </c>
-      <c r="D21" s="46" t="s">
-        <v>278</v>
-      </c>
-      <c r="E21" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" s="136" t="s">
-        <v>117</v>
-      </c>
-      <c r="G21" s="136"/>
-      <c r="H21" s="136"/>
-      <c r="I21" s="116" t="s">
-        <v>152</v>
-      </c>
-      <c r="J21" s="116"/>
-      <c r="K21" s="116"/>
-      <c r="L21" s="116" t="s">
-        <v>152</v>
-      </c>
-      <c r="M21" s="116"/>
-      <c r="N21" s="116"/>
-      <c r="O21" s="138" t="s">
-        <v>279</v>
-      </c>
-      <c r="Q21" s="140"/>
-    </row>
-    <row r="22" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="136" t="s">
-        <v>280</v>
-      </c>
-      <c r="B22" s="137" t="s">
-        <v>281</v>
-      </c>
-      <c r="C22" s="137" t="s">
-        <v>282</v>
-      </c>
-      <c r="D22" s="46" t="s">
-        <v>283</v>
-      </c>
-      <c r="E22" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="F22" s="136" t="s">
-        <v>117</v>
-      </c>
-      <c r="G22" s="136"/>
-      <c r="H22" s="136"/>
-      <c r="I22" s="116" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="116"/>
-      <c r="K22" s="116"/>
-      <c r="L22" s="116" t="s">
-        <v>152</v>
-      </c>
-      <c r="M22" s="116"/>
-      <c r="N22" s="116"/>
-      <c r="O22" s="138" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q22" s="140"/>
-    </row>
-    <row r="23" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="136" t="s">
-        <v>285</v>
-      </c>
-      <c r="B23" s="137" t="s">
-        <v>261</v>
-      </c>
-      <c r="C23" s="137" t="s">
-        <v>286</v>
-      </c>
-      <c r="D23" s="46" t="s">
-        <v>287</v>
-      </c>
-      <c r="E23" s="46" t="s">
-        <v>100</v>
-      </c>
-      <c r="F23" s="136" t="s">
-        <v>117</v>
-      </c>
-      <c r="G23" s="136"/>
-      <c r="H23" s="136"/>
-      <c r="I23" s="116" t="s">
-        <v>152</v>
-      </c>
-      <c r="J23" s="116"/>
-      <c r="K23" s="116"/>
-      <c r="L23" s="116" t="s">
-        <v>152</v>
-      </c>
-      <c r="M23" s="116"/>
-      <c r="N23" s="116"/>
-      <c r="O23" s="138" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q23" s="140"/>
-    </row>
-    <row r="24" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="136" t="s">
-        <v>289</v>
-      </c>
-      <c r="B24" s="137" t="s">
-        <v>290</v>
-      </c>
-      <c r="C24" s="137" t="s">
-        <v>291</v>
-      </c>
-      <c r="D24" s="46" t="s">
-        <v>292</v>
-      </c>
-      <c r="E24" s="46" t="s">
-        <v>103</v>
-      </c>
-      <c r="F24" s="136" t="s">
-        <v>117</v>
-      </c>
-      <c r="G24" s="136"/>
-      <c r="H24" s="136"/>
-      <c r="I24" s="116" t="s">
-        <v>152</v>
-      </c>
-      <c r="J24" s="116"/>
-      <c r="K24" s="116"/>
-      <c r="L24" s="116" t="s">
-        <v>152</v>
-      </c>
-      <c r="M24" s="116"/>
-      <c r="N24" s="116"/>
-      <c r="O24" s="138" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q24" s="140"/>
-    </row>
-    <row r="25" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="136" t="s">
-        <v>294</v>
-      </c>
-      <c r="B25" s="137" t="s">
-        <v>295</v>
-      </c>
-      <c r="C25" s="137" t="s">
-        <v>296</v>
-      </c>
-      <c r="D25" s="46" t="s">
-        <v>297</v>
-      </c>
-      <c r="E25" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="F25" s="136" t="s">
-        <v>117</v>
-      </c>
-      <c r="G25" s="136"/>
-      <c r="H25" s="136"/>
-      <c r="I25" s="116" t="s">
-        <v>152</v>
-      </c>
-      <c r="J25" s="116"/>
-      <c r="K25" s="116"/>
-      <c r="L25" s="116" t="s">
-        <v>152</v>
-      </c>
-      <c r="M25" s="116"/>
-      <c r="N25" s="116"/>
-      <c r="O25" s="138" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q25" s="140"/>
-    </row>
-    <row r="26" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="136" t="s">
-        <v>299</v>
-      </c>
-      <c r="B26" s="137" t="s">
-        <v>300</v>
-      </c>
-      <c r="C26" s="137" t="s">
-        <v>301</v>
-      </c>
-      <c r="D26" s="46" t="s">
-        <v>302</v>
-      </c>
-      <c r="E26" s="46" t="s">
-        <v>109</v>
-      </c>
-      <c r="F26" s="136" t="s">
-        <v>117</v>
-      </c>
-      <c r="G26" s="136"/>
-      <c r="H26" s="136"/>
-      <c r="I26" s="116" t="s">
-        <v>152</v>
-      </c>
-      <c r="J26" s="116"/>
-      <c r="K26" s="116"/>
-      <c r="L26" s="116" t="s">
-        <v>152</v>
-      </c>
-      <c r="M26" s="116"/>
-      <c r="N26" s="116"/>
-      <c r="O26" s="138" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q26" s="140"/>
-    </row>
+      <c r="A18" s="50"/>
+    </row>
+    <row r="19" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="22" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="26" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:E2"/>
